--- a/test.xlsx
+++ b/test.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\dansong\config-gen-aruba\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CA1A2F-A8C8-4E11-BA70-0EFDDF44430F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276C8C14-3DB8-4543-896B-52492512826E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33210" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{BA333789-6A28-43C5-97BC-959B97348293}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BA333789-6A28-43C5-97BC-959B97348293}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="ss" sheetId="1" r:id="rId2"/>
+    <sheet name="ss" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
   <si>
     <t>port</t>
   </si>
@@ -163,6 +163,45 @@
   </si>
   <si>
     <t>530</t>
+  </si>
+  <si>
+    <t>Desktop@ucl</t>
+  </si>
+  <si>
+    <t>QSC 110F LAN A</t>
+  </si>
+  <si>
+    <t>QSC 110F LAN B</t>
+  </si>
+  <si>
+    <t>Ampetonic - DANTE</t>
+  </si>
+  <si>
+    <t>Ampetonic - LAN</t>
+  </si>
+  <si>
+    <t>Crestron NVX 363-C</t>
+  </si>
+  <si>
+    <t>Crestron NVX D30-C</t>
+  </si>
+  <si>
+    <t>Crestron NVX E30-C</t>
+  </si>
+  <si>
+    <t>Crestron NVX 384-C</t>
+  </si>
+  <si>
+    <t>Crestron NVX 360-C</t>
+  </si>
+  <si>
+    <t>707</t>
+  </si>
+  <si>
+    <t>SG46LHR0CQ</t>
+  </si>
+  <si>
+    <t>172.22.29.201</t>
   </si>
 </sst>
 </file>
@@ -253,7 +292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -320,12 +359,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -361,7 +424,27 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -696,287 +779,456 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D7DFEE-9059-44D9-AD2E-2C1D02494E9E}">
-  <dimension ref="A1:C26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507EB172-38FB-4E1B-BA83-5B54CD117620}">
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="12">
+      <c r="D2" s="13">
+        <v>807</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="13">
+        <v>909</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="13">
+        <v>909</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="13">
+        <v>909</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="13">
+        <v>909</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="13">
+        <v>712</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="13">
+        <v>12</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="13">
+        <v>909</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="10">
+        <v>36892</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="13">
+        <v>909</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="13">
         <v>530</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E11" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="13">
         <v>530</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E12" s="20" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="12">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="13">
+        <v>909</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="13">
+        <v>909</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="21">
+        <v>909</v>
+      </c>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="13">
         <v>530</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="12">
-        <v>909</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="12">
-        <v>909</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="12">
-        <v>909</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="12">
-        <v>909</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="12">
-        <v>909</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="12">
-        <v>909</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="12">
-        <v>909</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="12">
-        <v>909</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="12">
-        <v>909</v>
-      </c>
-      <c r="C13" s="6"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="12">
-        <v>909</v>
-      </c>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="13">
-        <v>62</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="12">
-        <v>712</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="12">
-        <v>909</v>
-      </c>
-      <c r="C17" s="6"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="D17" s="13">
+        <v>707</v>
+      </c>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="12">
-        <v>909</v>
-      </c>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="D18" s="13">
+        <v>707</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="12">
-        <v>909</v>
-      </c>
-      <c r="C19" s="6"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="D19" s="13">
+        <v>707</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="12">
-        <v>909</v>
-      </c>
-      <c r="C20" s="6"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="D20" s="13">
+        <v>707</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="12">
-        <v>909</v>
-      </c>
-      <c r="C21" s="6"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="D21" s="13">
+        <v>707</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="12">
-        <v>909</v>
-      </c>
-      <c r="C22" s="6"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="D22" s="13">
+        <v>707</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="12">
-        <v>712</v>
-      </c>
-      <c r="C23" s="6"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="D23" s="13">
+        <v>707</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="6"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="D24" s="13">
+        <v>707</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="D25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B15" r:id="rId1" display="D@UCL - TBC" xr:uid="{8D6392BC-E246-4719-B9AA-47931E9D1B38}"/>
+    <hyperlink ref="D15" r:id="rId1" display="D@UCL - TBC" xr:uid="{DB200FF6-EDA6-4DB3-986B-897E9BE1BA07}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507EB172-38FB-4E1B-BA83-5B54CD117620}">
-  <dimension ref="A1:E26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D7DFEE-9059-44D9-AD2E-2C1D02494E9E}">
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -987,164 +1239,161 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="13">
         <v>530</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="13">
         <v>530</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="13">
         <v>530</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <v>909</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <v>909</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <v>909</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <v>909</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="13">
         <v>909</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="10">
-        <v>36892</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <v>909</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <v>909</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <v>909</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <v>909</v>
       </c>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <v>909</v>
       </c>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="13">
-        <v>62</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="14">
+        <v>37</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="13">
         <v>712</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -1155,7 +1404,7 @@
       <c r="A17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="13">
         <v>909</v>
       </c>
       <c r="C17" s="6"/>
@@ -1164,7 +1413,7 @@
       <c r="A18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="13">
         <v>909</v>
       </c>
       <c r="C18" s="6"/>
@@ -1173,7 +1422,7 @@
       <c r="A19" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="13">
         <v>909</v>
       </c>
       <c r="C19" s="6"/>
@@ -1182,7 +1431,7 @@
       <c r="A20" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="13">
         <v>909</v>
       </c>
       <c r="C20" s="6"/>
@@ -1191,7 +1440,7 @@
       <c r="A21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="13">
         <v>909</v>
       </c>
       <c r="C21" s="6"/>
@@ -1200,7 +1449,7 @@
       <c r="A22" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="13">
         <v>909</v>
       </c>
       <c r="C22" s="6"/>
@@ -1209,7 +1458,7 @@
       <c r="A23" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="13">
         <v>712</v>
       </c>
       <c r="C23" s="6"/>
@@ -1218,7 +1467,7 @@
       <c r="A24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="13" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="6"/>
@@ -1227,7 +1476,7 @@
       <c r="A25" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="12"/>
+      <c r="B25" s="13"/>
       <c r="C25" s="7" t="s">
         <v>14</v>
       </c>
@@ -1238,9 +1487,9 @@
       <c r="C26" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B15" r:id="rId1" display="D@UCL - TBC" xr:uid="{DB200FF6-EDA6-4DB3-986B-897E9BE1BA07}"/>
+    <hyperlink ref="B15" r:id="rId1" display="D@UCL - TBC" xr:uid="{8D6392BC-E246-4719-B9AA-47931E9D1B38}"/>
+    <hyperlink ref="C15" r:id="rId2" xr:uid="{8AFF602D-F4E5-4B66-BC5B-76BD96E82878}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
